--- a/data/trans_camb/P1803_2016_2023-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1803_2016_2023-Clase-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,33</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>8,97</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,87</t>
+          <t>7,0</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 10,5</t>
+          <t>1,12; 9,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 13,44</t>
+          <t>4,54; 12,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 10,38</t>
+          <t>3,86; 9,65</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>128,4%</t>
+          <t>119,83%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105,93%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,75; 197,03</t>
+          <t>10,77; 170,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,55; 249,01</t>
+          <t>43,38; 253,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50,16; 170,72</t>
+          <t>42,46; 163,64</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,53</t>
+          <t>4,05</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>6,4</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>5,0</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,73</t>
+          <t>0,63; 7,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 10,98</t>
+          <t>2,29; 10,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 8,08</t>
+          <t>2,42; 7,93</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>121,56%</t>
+          <t>108,83%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>80,73%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,3; 325,66</t>
+          <t>8,75; 309,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,92; 162,45</t>
+          <t>18,51; 154,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,78; 171,59</t>
+          <t>29,41; 165,3</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>38,31</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>2,21</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31,03</t>
+          <t>4,68</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 73,44</t>
+          <t>2,19; 9,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 7,2</t>
+          <t>-3,13; 7,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 63,32</t>
+          <t>1,91; 7,82</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>825,77%</t>
+          <t>119,35%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>599,69%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>79,07; 2613,84</t>
+          <t>33,13; 298,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,11; 171,71</t>
+          <t>-33,13; 194,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,46; 1805,29</t>
+          <t>30,71; 206,93</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,29</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,39</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,45</t>
+          <t>2,95</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,39</t>
+          <t>0,13; 4,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 5,53</t>
+          <t>1,61; 6,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 4,23</t>
+          <t>1,31; 4,51</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,92; 114,29</t>
+          <t>2,18; 113,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,97; 99,56</t>
+          <t>21,41; 130,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,67; 92,16</t>
+          <t>21,37; 101,29</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>4,08</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>3,43</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 6,07</t>
+          <t>-0,31; 5,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,55</t>
+          <t>1,85; 6,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,05</t>
+          <t>1,63; 5,04</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>87,38%</t>
         </is>
       </c>
     </row>
@@ -1001,24 +1001,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,44; 230,22</t>
+          <t>-8,81; 188,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11,02; 161,73</t>
+          <t>30,1; 191,75</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26,29; 154,1</t>
+          <t>31,68; 161,64</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>1,64</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 9,6</t>
+          <t>-2,57; 8,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,72</t>
+          <t>-0,43; 3,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,06</t>
+          <t>-0,17; 3,8</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-71,5; 373,1</t>
+          <t>-63,5; 401,42</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 117,01</t>
+          <t>-9,29; 133,09</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 129,74</t>
+          <t>-5,17; 120,38</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>10,54</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7,18</t>
+          <t>4,02</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,51; 26,39</t>
+          <t>2,29; 4,77</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,34</t>
+          <t>3,39; 5,63</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,69; 18,95</t>
+          <t>3,09; 4,79</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>231,78%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>142,02%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>73,55; 671,75</t>
+          <t>44,4; 116,42</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>36,6; 105,69</t>
+          <t>55,85; 115,09</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>71,47; 392,33</t>
+          <t>56,72; 102,04</t>
         </is>
       </c>
     </row>
